--- a/sheets/조재수대금교본/검수/민요 연곡.xlsx
+++ b/sheets/조재수대금교본/검수/민요 연곡.xlsx
@@ -2298,9 +2298,7 @@
       <c r="I4" s="22"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z
-Z
-–</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K4" s="22"/>
@@ -2414,11 +2412,7 @@
         </is>
       </c>
       <c r="K6" s="22"/>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L6" s="21"/>
       <c r="M6" s="22"/>
       <c r="N6" s="21"/>
       <c r="O6" s="22"/>
@@ -2486,8 +2480,7 @@
         <is>
           <t xml:space="preserve">潢
 △
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="G8" s="22"/>
@@ -2573,8 +2566,7 @@
         <is>
           <t xml:space="preserve">潢
 △
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="G10" s="22"/>
@@ -2592,23 +2584,11 @@
         </is>
       </c>
       <c r="K10" s="22"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L10" s="21"/>
       <c r="M10" s="22"/>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N10" s="21"/>
       <c r="O10" s="22"/>
-      <c r="P10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P10" s="21"/>
       <c r="Q10" s="22"/>
     </row>
     <row r="11" ht="118.46" customHeight="true">

--- a/sheets/조재수대금교본/검수/민요 연곡.xlsx
+++ b/sheets/조재수대금교본/검수/민요 연곡.xlsx
@@ -2298,7 +2298,9 @@
       <c r="I4" s="22"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">Z
+Z
+–</t>
         </is>
       </c>
       <c r="K4" s="22"/>

--- a/sheets/조재수대금교본/검수/민요 연곡.xlsx
+++ b/sheets/조재수대금교본/검수/민요 연곡.xlsx
@@ -2157,28 +2157,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="59.7" customHeight="true">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="118.46" customHeight="true">
+    <row r="3" ht="128.07" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="118.46" customHeight="true">
+    <row r="4" ht="128.07" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
       <c r="P4" s="21"/>
       <c r="Q4" s="22"/>
     </row>
-    <row r="5" ht="118.46" customHeight="true">
+    <row r="5" ht="128.07" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
       <c r="P5" s="21"/>
       <c r="Q5" s="22"/>
     </row>
-    <row r="6" ht="118.46" customHeight="true">
+    <row r="6" ht="128.07" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
       <c r="P6" s="21"/>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="118.46" customHeight="true">
+    <row r="7" ht="128.07" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="22"/>
@@ -2466,7 +2466,7 @@
       <c r="P7" s="21"/>
       <c r="Q7" s="22"/>
     </row>
-    <row r="8" ht="118.46" customHeight="true">
+    <row r="8" ht="128.07" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="22"/>
@@ -2509,7 +2509,7 @@
       <c r="P8" s="21"/>
       <c r="Q8" s="22"/>
     </row>
-    <row r="9" ht="118.46" customHeight="true">
+    <row r="9" ht="128.07" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -2552,7 +2552,7 @@
       <c r="P9" s="21"/>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="118.46" customHeight="true">
+    <row r="10" ht="128.07" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="22"/>
@@ -2593,7 +2593,7 @@
       <c r="P10" s="21"/>
       <c r="Q10" s="22"/>
     </row>
-    <row r="11" ht="118.46" customHeight="true">
+    <row r="11" ht="128.07" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -2618,6 +2618,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="67"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
 </worksheet>
 </file>